--- a/gangho/docs/상성표.xlsx
+++ b/gangho/docs/상성표.xlsx
@@ -1144,7 +1144,7 @@
         <v>-0.04</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>0.3</v>
